--- a/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
@@ -112,7 +112,9 @@
 13  雷霆级勋章
 14  特殊类勋章
 21  上古T1勋章
-22  上古T2勋章</t>
+22  上古T2勋章
+23  上古T3勋章
+24  上古T4勋章</t>
         </r>
       </text>
     </comment>
@@ -165,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="44">
   <si>
     <t>Id</t>
   </si>
@@ -285,6 +287,18 @@
   </si>
   <si>
     <t>星辰勋章</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>战神凭证</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>帝释天勋章</t>
   </si>
 </sst>
 </file>
@@ -565,12 +579,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1488,7 +1502,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{EC265765-FB90-4D6C-A210-A95F43B2B380}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{1EB9B355-501D-4A30-85DC-0E5FB78B798D}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -2640,7 +2654,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.625" style="1" customWidth="1"/>
@@ -3031,6 +3045,56 @@
         <v>19</v>
       </c>
     </row>
+    <row r="18" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A18" s="1"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8">
+        <v>13</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A19" s="1"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8">
+        <v>14</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -226,34 +226,37 @@
     <t>30</t>
   </si>
   <si>
+    <t>7;1@8;1</t>
+  </si>
+  <si>
+    <t>荣誉级勋章2级</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>7;1@8;1@9;1@10;1@11;1</t>
+  </si>
+  <si>
+    <t>荣誉级勋章3级</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>荣誉级勋章4级</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>圣战级勋章1级</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>1;1@2;1</t>
-  </si>
-  <si>
-    <t>荣誉级勋章2级</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1;1@2;2</t>
-  </si>
-  <si>
-    <t>荣誉级勋章3级</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>荣誉级勋章4级</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>圣战级勋章1级</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>圣战级勋章2级</t>
@@ -2844,7 +2847,7 @@
         <v>18</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -2869,7 +2872,7 @@
         <v>18</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -2885,16 +2888,16 @@
         <v>21</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -2904,13 +2907,13 @@
         <v>7</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>16</v>
@@ -2919,7 +2922,7 @@
         <v>18</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -2929,13 +2932,13 @@
         <v>8</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>21</v>
@@ -2954,13 +2957,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>24</v>
@@ -2977,13 +2980,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>26</v>
@@ -2992,7 +2995,7 @@
         <v>18</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -3002,13 +3005,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>28</v>
@@ -3017,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -3027,22 +3030,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -3052,13 +3055,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>28</v>
@@ -3067,7 +3070,7 @@
         <v>18</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
@@ -3077,22 +3080,22 @@
         <v>14</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
@@ -118,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="1">
+    <comment ref="I3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -140,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="1">
+    <comment ref="J3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -178,7 +178,10 @@
     <t>勋章小类型</t>
   </si>
   <si>
-    <t>勋章名字</t>
+    <t>勋章道具id</t>
+  </si>
+  <si>
+    <t>勋章名字（可以不用读道具表）</t>
   </si>
   <si>
     <t>消耗声望值</t>
@@ -196,6 +199,9 @@
     <t>SubType</t>
   </si>
   <si>
+    <t>ItemId</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -220,6 +226,9 @@
     <t>11</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>荣誉级勋章1级</t>
   </si>
   <si>
@@ -229,6 +238,9 @@
     <t>7;1@8;1</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>荣誉级勋章2级</t>
   </si>
   <si>
@@ -238,42 +250,48 @@
     <t>7;1@8;1@9;1@10;1@11;1</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>荣誉级勋章3级</t>
   </si>
   <si>
-    <t>13</t>
+    <t>16</t>
   </si>
   <si>
     <t>荣誉级勋章4级</t>
   </si>
   <si>
-    <t>14</t>
+    <t>17</t>
   </si>
   <si>
     <t>圣战级勋章1级</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>1;1@2;1</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>圣战级勋章2级</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>白虎印</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>朱雀印</t>
   </si>
   <si>
@@ -286,19 +304,25 @@
     <t>无双勋章</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>荒古勋章</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>星辰勋章</t>
   </si>
   <si>
-    <t>23</t>
+    <t>25</t>
   </si>
   <si>
     <t>战神凭证</t>
   </si>
   <si>
-    <t>24</t>
+    <t>26</t>
   </si>
   <si>
     <t>帝释天勋章</t>
@@ -2657,30 +2681,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.25" customWidth="1"/>
     <col min="3" max="3" width="9.375" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="4" max="4" width="31.75" customWidth="1"/>
     <col min="5" max="5" width="23.125" customWidth="1"/>
-    <col min="6" max="6" width="30.625" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="9" width="30.625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="30.625" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="10" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:9">
+    <row r="1" ht="14.25" spans="1:10">
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
-    <row r="2" customHeight="1" spans="1:9">
+    <row r="2" customHeight="1" spans="1:10">
       <c r="D2" s="3"/>
     </row>
-    <row r="3" ht="14.25" spans="1:9">
+    <row r="3" ht="14.25" spans="1:10">
       <c r="B3" s="1"/>
       <c r="C3" s="4" t="s">
         <v>0</v>
@@ -2703,399 +2729,450 @@
       <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:9">
+    <row r="4" ht="18.75" customHeight="1" spans="1:10">
       <c r="B4" s="1"/>
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="1:9">
+    <row r="5" ht="20.1" customHeight="1" spans="1:10">
       <c r="B5" s="1"/>
       <c r="C5" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="6" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A6" s="1"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="7" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A7" s="1"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>22</v>
+      <c r="J7" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="8" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A8" s="1"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="7"/>
+        <v>19</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="7"/>
     </row>
-    <row r="9" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="9" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A9" s="1"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8">
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="10" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="10" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A10" s="1"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8">
         <v>5</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>29</v>
+      <c r="J10" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="11" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A11" s="1"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8">
         <v>6</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>22</v>
+      <c r="J11" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="12" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8">
         <v>7</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="13" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="13" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A13" s="1"/>
       <c r="B13" s="7"/>
       <c r="C13" s="8">
         <v>8</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>22</v>
+      <c r="J13" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="14" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A14" s="1"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8">
         <v>9</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="7"/>
+        <v>19</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="7"/>
     </row>
-    <row r="15" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="15" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A15" s="1"/>
       <c r="B15" s="7"/>
       <c r="C15" s="8">
         <v>10</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="16" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A16" s="1"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8">
         <v>11</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="17" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A17" s="1"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8">
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="18" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A18" s="1"/>
       <c r="B18" s="7"/>
       <c r="C18" s="8">
         <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="19" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+    <row r="19" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
       <c r="A19" s="1"/>
       <c r="B19" s="7"/>
       <c r="C19" s="8">
         <v>14</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
@@ -1529,7 +1529,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{1EB9B355-501D-4A30-85DC-0E5FB78B798D}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{FA008827-8847-42FE-ABA6-554AFA68A625}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>

--- a/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -235,7 +235,7 @@
     <t>30</t>
   </si>
   <si>
-    <t>7;1@8;1</t>
+    <t>10000;1@10001;1</t>
   </si>
   <si>
     <t>14</t>
@@ -247,7 +247,7 @@
     <t>12</t>
   </si>
   <si>
-    <t>7;1@8;1@9;1@10;1@11;1</t>
+    <t>10000;1@10001;1@10002;1</t>
   </si>
   <si>
     <t>15</t>
@@ -266,9 +266,6 @@
   </si>
   <si>
     <t>圣战级勋章1级</t>
-  </si>
-  <si>
-    <t>1;1@2;1</t>
   </si>
   <si>
     <t>18</t>
@@ -606,12 +603,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1529,7 +1526,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{FA008827-8847-42FE-ABA6-554AFA68A625}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{DCBF5AE4-4E8D-48B2-9187-551D6C001BBF}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -2922,7 +2919,7 @@
         <v>21</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
@@ -2938,10 +2935,10 @@
         <v>25</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>29</v>
@@ -2960,16 +2957,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>18</v>
@@ -2978,7 +2975,7 @@
         <v>21</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
@@ -2988,16 +2985,16 @@
         <v>8</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="F13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -3016,16 +3013,16 @@
         <v>9</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>19</v>
@@ -3042,16 +3039,16 @@
         <v>10</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>23</v>
@@ -3060,7 +3057,7 @@
         <v>21</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
@@ -3070,16 +3067,16 @@
         <v>11</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>27</v>
@@ -3088,7 +3085,7 @@
         <v>21</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
@@ -3098,16 +3095,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>48</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>29</v>
@@ -3116,7 +3113,7 @@
         <v>21</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
@@ -3126,16 +3123,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>27</v>
@@ -3144,7 +3141,7 @@
         <v>21</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="20.1" customHeight="1" spans="1:10">
@@ -3154,16 +3151,16 @@
         <v>14</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>29</v>
@@ -3172,7 +3169,7 @@
         <v>21</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MedalExchangeConfig.xlsx
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -226,100 +226,124 @@
     <t>11</t>
   </si>
   <si>
+    <t>13035</t>
+  </si>
+  <si>
+    <t>荣誉级勋章1级</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>10000;1@10001;1</t>
+  </si>
+  <si>
+    <t>13036</t>
+  </si>
+  <si>
+    <t>荣誉级勋章2级</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10000;1@10001;1@10002;1</t>
+  </si>
+  <si>
+    <t>13037</t>
+  </si>
+  <si>
+    <t>荣誉级勋章3级</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
-    <t>荣誉级勋章1级</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>10000;1@10001;1</t>
+    <t>13038</t>
+  </si>
+  <si>
+    <t>荣誉级勋章4级</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>荣誉级勋章2级</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>10000;1@10001;1@10002;1</t>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>圣战级勋章1级</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>荣誉级勋章3级</t>
+    <t>13040</t>
+  </si>
+  <si>
+    <t>圣战级勋章2级</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>荣誉级勋章4级</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>圣战级勋章1级</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>圣战级勋章2级</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>19</t>
+    <t>13041</t>
   </si>
   <si>
     <t>白虎印</t>
   </si>
   <si>
-    <t>20</t>
+    <t>13042</t>
   </si>
   <si>
     <t>朱雀印</t>
   </si>
   <si>
+    <t>13043</t>
+  </si>
+  <si>
     <t>青龙印</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
+    <t>13044</t>
+  </si>
+  <si>
     <t>无双勋章</t>
   </si>
   <si>
+    <t>13045</t>
+  </si>
+  <si>
+    <t>荒古勋章</t>
+  </si>
+  <si>
+    <t>13046</t>
+  </si>
+  <si>
+    <t>星辰勋章</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>荒古勋章</t>
+    <t>13047</t>
+  </si>
+  <si>
+    <t>战神凭证</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>星辰勋章</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>战神凭证</t>
-  </si>
-  <si>
-    <t>26</t>
+    <t>13048</t>
   </si>
   <si>
     <t>帝释天勋章</t>
@@ -2859,7 +2883,7 @@
         <v>28</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>21</v>
@@ -2879,13 +2903,13 @@
         <v>18</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>21</v>
@@ -2907,13 +2931,13 @@
         <v>25</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>21</v>
@@ -2935,13 +2959,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>21</v>
@@ -2957,16 +2981,16 @@
         <v>7</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>18</v>
@@ -2985,16 +3009,16 @@
         <v>8</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -3013,19 +3037,19 @@
         <v>9</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>21</v>
@@ -3039,19 +3063,19 @@
         <v>10</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>21</v>
@@ -3067,19 +3091,19 @@
         <v>11</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>21</v>
@@ -3095,19 +3119,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>21</v>
@@ -3123,19 +3147,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>21</v>
@@ -3151,19 +3175,19 @@
         <v>14</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>21</v>
